--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-de-biologie-de-seconde-intention.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-de-biologie-de-seconde-intention.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-de-biologie-de-seconde-intention.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-de-biologie-de-seconde-intention.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-de-biologie-de-seconde-intention.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-de-biologie-de-seconde-intention.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-de-biologie-de-seconde-intention.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-de-biologie-de-seconde-intention.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3013" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3015" uniqueCount="325">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -475,10 +475,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -3422,7 +3425,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>148</v>
       </c>
@@ -3441,7 +3444,7 @@
         <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>74</v>
@@ -3452,8 +3455,12 @@
       <c r="K21" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+      <c r="L21" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3523,10 +3530,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3540,7 +3547,7 @@
         <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>74</v>
@@ -3549,13 +3556,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3606,7 +3613,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3626,10 +3633,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3725,12 +3732,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3740,13 +3747,13 @@
         <v>62</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>74</v>
@@ -3759,7 +3766,7 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3771,7 +3778,7 @@
         <v>74</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>74</v>
@@ -3810,7 +3817,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3828,28 +3835,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>74</v>
@@ -3862,7 +3869,7 @@
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3874,7 +3881,7 @@
         <v>74</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>74</v>
@@ -3913,7 +3920,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3933,17 +3940,17 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3965,7 +3972,7 @@
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3977,7 +3984,7 @@
         <v>74</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>74</v>
@@ -4016,7 +4023,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4036,17 +4043,17 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
@@ -4068,7 +4075,7 @@
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4119,7 +4126,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4137,28 +4144,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -4171,7 +4178,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4183,7 +4190,7 @@
         <v>74</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>74</v>
@@ -4222,7 +4229,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4242,10 +4249,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4268,11 +4275,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4323,7 +4330,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4343,10 +4350,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4373,7 +4380,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4424,7 +4431,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4444,17 +4451,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4472,11 +4479,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4527,7 +4534,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4547,17 +4554,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4575,11 +4582,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4630,7 +4637,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4650,17 +4657,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4678,11 +4685,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4733,7 +4740,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4753,10 +4760,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4770,7 +4777,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4779,13 +4786,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4836,7 +4843,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4856,10 +4863,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4873,7 +4880,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -4882,13 +4889,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4939,7 +4946,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4959,10 +4966,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4985,7 +4992,7 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -5038,7 +5045,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5058,10 +5065,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5117,25 +5124,25 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5155,10 +5162,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5181,7 +5188,7 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
@@ -5234,7 +5241,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5254,10 +5261,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5280,7 +5287,7 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -5333,7 +5340,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5353,10 +5360,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5379,7 +5386,7 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
@@ -5432,7 +5439,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5452,10 +5459,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5469,7 +5476,7 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5478,7 +5485,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -5519,7 +5526,7 @@
         <v>74</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -5529,7 +5536,7 @@
         <v>123</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5549,13 +5556,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>74</v>
@@ -5577,7 +5584,7 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -5630,7 +5637,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5650,10 +5657,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5751,10 +5758,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5852,10 +5859,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5953,10 +5960,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6054,10 +6061,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6157,10 +6164,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6260,10 +6267,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6363,10 +6370,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6466,10 +6473,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6567,10 +6574,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6600,7 +6607,7 @@
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
@@ -6626,7 +6633,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>74</v>
@@ -6644,7 +6651,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6664,10 +6671,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6701,7 +6708,7 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>74</v>
@@ -6743,7 +6750,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6763,10 +6770,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6789,7 +6796,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6842,7 +6849,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6862,10 +6869,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6888,7 +6895,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -6941,7 +6948,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6961,10 +6968,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6987,10 +6994,10 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
@@ -7042,7 +7049,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7062,10 +7069,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7088,7 +7095,7 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -7141,7 +7148,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7161,10 +7168,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7187,7 +7194,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7240,7 +7247,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7260,10 +7267,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7286,7 +7293,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7339,7 +7346,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7359,10 +7366,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7385,7 +7392,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7438,7 +7445,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7458,10 +7465,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7484,7 +7491,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7537,7 +7544,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7557,10 +7564,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7583,7 +7590,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7636,7 +7643,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7656,13 +7663,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>74</v>
@@ -7684,7 +7691,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7737,7 +7744,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7757,10 +7764,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7858,10 +7865,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7959,10 +7966,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8060,10 +8067,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8161,10 +8168,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8264,10 +8271,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8367,10 +8374,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8470,10 +8477,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8573,10 +8580,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8674,10 +8681,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8707,7 +8714,7 @@
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
@@ -8733,7 +8740,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -8751,7 +8758,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8771,10 +8778,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8808,7 +8815,7 @@
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>74</v>
@@ -8850,7 +8857,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8870,10 +8877,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8896,7 +8903,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -8949,7 +8956,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -8969,10 +8976,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8995,7 +9002,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9048,7 +9055,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9068,10 +9075,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9094,7 +9101,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9147,7 +9154,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9167,10 +9174,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9193,7 +9200,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9246,7 +9253,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9266,10 +9273,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9292,10 +9299,10 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
@@ -9347,7 +9354,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9367,10 +9374,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9393,7 +9400,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9446,7 +9453,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9466,10 +9473,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9492,7 +9499,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9545,7 +9552,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9565,10 +9572,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9591,7 +9598,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9644,7 +9651,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9664,10 +9671,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9690,7 +9697,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -9743,7 +9750,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9763,10 +9770,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9789,7 +9796,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -9842,7 +9849,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9862,10 +9869,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9963,10 +9970,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10064,10 +10071,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10165,10 +10172,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10266,10 +10273,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10369,10 +10376,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10472,10 +10479,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10575,10 +10582,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10678,10 +10685,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10779,10 +10786,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10809,7 +10816,7 @@
       </c>
       <c r="L94" s="2"/>
       <c r="M94" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -10818,7 +10825,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>74</v>
@@ -10860,7 +10867,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -10880,10 +10887,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -10917,7 +10924,7 @@
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>74</v>
@@ -10959,7 +10966,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -10979,10 +10986,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11005,7 +11012,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11058,7 +11065,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-de-biologie-de-seconde-intention.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-de-biologie-de-seconde-intention.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-de-biologie-de-seconde-intention.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-de-biologie-de-seconde-intention.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
